--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v6/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/contrary_v6/Contrary(P)Body(N).xlsx
@@ -33651,13 +33651,13 @@
         <v>65</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.431373</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5751633986928104</v>
+        <v>0.575163</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4929971988795518</v>
+        <v>0.492997</v>
       </c>
       <c r="O2" t="n">
         <v>0.638</v>
@@ -33710,13 +33710,13 @@
         <v>65</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.431373</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5751633986928104</v>
+        <v>0.575163</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4929971988795518</v>
+        <v>0.492997</v>
       </c>
       <c r="O3" t="n">
         <v>0.638</v>
@@ -33769,13 +33769,13 @@
         <v>65</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.431373</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5751633986928104</v>
+        <v>0.575163</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4929971988795518</v>
+        <v>0.492997</v>
       </c>
       <c r="O4" t="n">
         <v>0.638</v>
